--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerSkuMapping.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>平台</t>
   </si>
@@ -58,6 +58,12 @@
     <t>匹配关系</t>
   </si>
   <si>
+    <t>产品标签</t>
+  </si>
+  <si>
+    <t>上传附件</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -98,6 +104,12 @@
   </si>
   <si>
     <t>{.matchResultStr}</t>
+  </si>
+  <si>
+    <t>{.labelUrlStr}</t>
+  </si>
+  <si>
+    <t>{.uploadLabelStr}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1113,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1122,11 +1134,11 @@
     <col min="4" max="4" width="42.575" customWidth="1"/>
     <col min="5" max="7" width="20.5083333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.75" customWidth="1"/>
-    <col min="9" max="11" width="19.125" customWidth="1"/>
-    <col min="12" max="14" width="18.625" customWidth="1"/>
+    <col min="9" max="13" width="19.125" customWidth="1"/>
+    <col min="14" max="16" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:14">
+    <row r="1" ht="35.25" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1169,49 +1181,61 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:14">
+    <row r="2" ht="21" customHeight="1" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="J2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="L2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerSkuMapping.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>平台</t>
   </si>
@@ -55,6 +55,12 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>父平台产品ID</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
     <t>匹配关系</t>
   </si>
   <si>
@@ -101,6 +107,12 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.platformParenSkutId}</t>
+  </si>
+  <si>
+    <t>{.platformStatusName}</t>
   </si>
   <si>
     <t>{.matchResultStr}</t>
@@ -1125,7 +1137,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1134,11 +1146,13 @@
     <col min="4" max="4" width="42.575" customWidth="1"/>
     <col min="5" max="7" width="20.5083333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.75" customWidth="1"/>
-    <col min="9" max="13" width="19.125" customWidth="1"/>
-    <col min="14" max="16" width="18.625" customWidth="1"/>
+    <col min="9" max="9" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="20.125" customWidth="1"/>
+    <col min="11" max="15" width="19.125" customWidth="1"/>
+    <col min="16" max="18" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:16">
+    <row r="1" ht="35.25" customHeight="1" spans="1:18">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1163,10 +1177,10 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -1187,55 +1201,67 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:16">
+    <row r="2" ht="21" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="I2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="K2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="L2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="N2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerSkuMapping.xlsx
@@ -109,7 +109,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.platformParenSkutId}</t>
+    <t>{.platformParentSpuNo}</t>
   </si>
   <si>
     <t>{.platformStatusName}</t>
@@ -1146,7 +1146,7 @@
     <col min="4" max="4" width="42.575" customWidth="1"/>
     <col min="5" max="7" width="20.5083333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.75" customWidth="1"/>
-    <col min="9" max="9" width="19.125" customWidth="1"/>
+    <col min="9" max="9" width="35.25" customWidth="1"/>
     <col min="10" max="10" width="20.125" customWidth="1"/>
     <col min="11" max="15" width="19.125" customWidth="1"/>
     <col min="16" max="18" width="18.625" customWidth="1"/>
